--- a/resolveIssues/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:56:38+00:00</t>
+    <t>2026-06-04T08:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -738,7 +738,8 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;code value="IHEPharmacyItemTypeList"/&gt;
+  &lt;system value="urn:oid:1.3.6.1.4.1.19376.1.9.2.2"/&gt;
+  &lt;code value="MTPItem"/&gt;
   &lt;display value="Ligne dans un plan de traitement"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>

--- a/resolveIssues/ig/StructureDefinition-fr-care-plan-document.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-care-plan-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T08:54:45+00:00</t>
+    <t>2026-06-04T14:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
